--- a/exports/trend_1d/DIXON_full_report.xlsx
+++ b/exports/trend_1d/DIXON_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q57"/>
+  <dimension ref="A1:U57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>16.42</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>43116</v>
+        <v>43117</v>
       </c>
       <c r="H2" t="n">
-        <v>740.75</v>
+        <v>728.8</v>
       </c>
       <c r="I2" t="n">
         <v>740.4518520675908</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K2" t="n">
-        <v>37.38</v>
+        <v>35.16</v>
       </c>
       <c r="L2" t="n">
         <v>4.35</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>43034</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>13.29</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>43194</v>
+        <v>43195</v>
       </c>
       <c r="H3" t="n">
-        <v>670.45</v>
+        <v>721.85</v>
       </c>
       <c r="I3" t="n">
         <v>715.1887317434</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K3" t="n">
-        <v>8.01</v>
+        <v>0.95</v>
       </c>
       <c r="L3" t="n">
         <v>14.76</v>
@@ -612,7 +647,7 @@
         <v>2.07</v>
       </c>
       <c r="N3" t="n">
-        <v>6.35</v>
+        <v>7.67</v>
       </c>
       <c r="O3" t="n">
         <v>-1.61</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>4</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>12.29</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>43250</v>
+        <v>43251</v>
       </c>
       <c r="H4" t="n">
-        <v>682.3</v>
+        <v>650.3</v>
       </c>
       <c r="I4" t="n">
         <v>657.2772573145387</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K4" t="n">
-        <v>-5.48</v>
+        <v>-9.91</v>
       </c>
       <c r="L4" t="n">
-        <v>6.66</v>
+        <v>12.03</v>
       </c>
       <c r="M4" t="n">
         <v>1.04</v>
       </c>
       <c r="N4" t="n">
-        <v>3.72</v>
+        <v>4.69</v>
       </c>
       <c r="O4" t="n">
         <v>7.67</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>12.33</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>43339</v>
+        <v>43340</v>
       </c>
       <c r="H5" t="n">
-        <v>537.05</v>
+        <v>573.1</v>
       </c>
       <c r="I5" t="n">
         <v>550.0690701894902</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K5" t="n">
-        <v>17.42</v>
+        <v>11.87</v>
       </c>
       <c r="L5" t="n">
         <v>5.59</v>
@@ -726,7 +785,7 @@
         <v>3.46</v>
       </c>
       <c r="N5" t="n">
-        <v>5.57</v>
+        <v>6.71</v>
       </c>
       <c r="O5" t="n">
         <v>-4.69</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>43279</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>13.97</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>43364</v>
+        <v>43367</v>
       </c>
       <c r="H6" t="n">
-        <v>530.9</v>
+        <v>520</v>
       </c>
       <c r="I6" t="n">
         <v>520.3321583536373</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K6" t="n">
-        <v>-7.36</v>
+        <v>-9.27</v>
       </c>
       <c r="L6" t="n">
-        <v>10.84</v>
+        <v>12.23</v>
       </c>
       <c r="M6" t="n">
         <v>3.22</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>13.51</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>43452</v>
+        <v>43453</v>
       </c>
       <c r="H7" t="n">
-        <v>406.15</v>
+        <v>424.35</v>
       </c>
       <c r="I7" t="n">
         <v>416.6476640255364</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K7" t="n">
-        <v>21.89</v>
+        <v>18.39</v>
       </c>
       <c r="L7" t="n">
         <v>2.12</v>
@@ -840,7 +923,7 @@
         <v>2.57</v>
       </c>
       <c r="N7" t="n">
-        <v>3.96</v>
+        <v>4.48</v>
       </c>
       <c r="O7" t="n">
         <v>-2.05</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>9.720000000000001</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>43573</v>
+        <v>43577</v>
       </c>
       <c r="H8" t="n">
-        <v>466.05</v>
+        <v>462.1</v>
       </c>
       <c r="I8" t="n">
         <v>465.5769337667283</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="K8" t="n">
-        <v>9.83</v>
+        <v>8.9</v>
       </c>
       <c r="L8" t="n">
         <v>6.21</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>5</v>
+      </c>
+      <c r="U8" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -933,28 +1040,28 @@
         <v>7.73</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>43608</v>
+        <v>43609</v>
       </c>
       <c r="H9" t="n">
-        <v>460.6</v>
+        <v>485.35</v>
       </c>
       <c r="I9" t="n">
         <v>478.5318020121973</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K9" t="n">
-        <v>0.32</v>
+        <v>-5.03</v>
       </c>
       <c r="L9" t="n">
-        <v>4.91</v>
+        <v>7.25</v>
       </c>
       <c r="M9" t="n">
         <v>1.56</v>
       </c>
       <c r="N9" t="n">
-        <v>3.6</v>
+        <v>5.37</v>
       </c>
       <c r="O9" t="n">
         <v>-0.85</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>43580</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,25 +1109,25 @@
         <v>11.47</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>43629</v>
+        <v>43630</v>
       </c>
       <c r="H10" t="n">
-        <v>451.7</v>
+        <v>441.65</v>
       </c>
       <c r="I10" t="n">
         <v>445.5046243314004</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K10" t="n">
-        <v>-6.93</v>
+        <v>-9</v>
       </c>
       <c r="L10" t="n">
         <v>10.58</v>
       </c>
       <c r="M10" t="n">
-        <v>1.13</v>
+        <v>1.66</v>
       </c>
       <c r="N10" t="n">
         <v>2.79</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>10.25</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>43690</v>
+        <v>43691</v>
       </c>
       <c r="H11" t="n">
-        <v>398.45</v>
+        <v>470.15</v>
       </c>
       <c r="I11" t="n">
         <v>422.3111642588923</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K11" t="n">
-        <v>9.779999999999999</v>
+        <v>-6.45</v>
       </c>
       <c r="L11" t="n">
         <v>8.550000000000001</v>
@@ -1068,7 +1199,7 @@
         <v>2.34</v>
       </c>
       <c r="N11" t="n">
-        <v>4.23</v>
+        <v>17.99</v>
       </c>
       <c r="O11" t="n">
         <v>-2.22</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>43643</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>25.5</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>43881</v>
+        <v>43885</v>
       </c>
       <c r="H12" t="n">
-        <v>870.45</v>
+        <v>824.65</v>
       </c>
       <c r="I12" t="n">
         <v>833.1720666232146</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="K12" t="n">
-        <v>85.14</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="L12" t="n">
         <v>13.61</v>
@@ -1125,7 +1268,7 @@
         <v>2.87</v>
       </c>
       <c r="N12" t="n">
-        <v>4.78</v>
+        <v>5.26</v>
       </c>
       <c r="O12" t="n">
         <v>17.99</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>130</v>
+        <v>131</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>43706</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>7</v>
+      </c>
+      <c r="U12" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>16.03</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>43942</v>
+        <v>43943</v>
       </c>
       <c r="H13" t="n">
-        <v>821.95</v>
+        <v>838.65</v>
       </c>
       <c r="I13" t="n">
         <v>833.5536197213487</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K13" t="n">
-        <v>0.33</v>
+        <v>-1.7</v>
       </c>
       <c r="L13" t="n">
         <v>10.23</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>22.49</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44095</v>
+        <v>44096</v>
       </c>
       <c r="H14" t="n">
-        <v>1780.2</v>
+        <v>1710.5</v>
       </c>
       <c r="I14" t="n">
         <v>1751.329873866813</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K14" t="n">
-        <v>112.27</v>
+        <v>103.96</v>
       </c>
       <c r="L14" t="n">
         <v>5.4</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>107</v>
+        <v>108</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>43951</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>6</v>
+      </c>
+      <c r="U14" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>21.8</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44126</v>
+        <v>44127</v>
       </c>
       <c r="H15" t="n">
-        <v>1899</v>
+        <v>1961.85</v>
       </c>
       <c r="I15" t="n">
         <v>1942.349071403781</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K15" t="n">
-        <v>-11.02</v>
+        <v>-14.69</v>
       </c>
       <c r="L15" t="n">
-        <v>12.83</v>
+        <v>16.34</v>
       </c>
       <c r="M15" t="n">
         <v>3.79</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>14.2</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44278</v>
+        <v>44279</v>
       </c>
       <c r="H16" t="n">
-        <v>3868.85</v>
+        <v>3676.4</v>
       </c>
       <c r="I16" t="n">
         <v>3711.967257278225</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="K16" t="n">
-        <v>97.2</v>
+        <v>87.39</v>
       </c>
       <c r="L16" t="n">
         <v>8.25</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>104</v>
+        <v>105</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>6</v>
+      </c>
+      <c r="U16" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>19.24</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44312</v>
+        <v>44313</v>
       </c>
       <c r="H17" t="n">
-        <v>3895.2</v>
+        <v>4033.7</v>
       </c>
       <c r="I17" t="n">
         <v>4008.504282407077</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K17" t="n">
-        <v>-5.95</v>
+        <v>-9.720000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>8.48</v>
+        <v>10.38</v>
       </c>
       <c r="M17" t="n">
         <v>4.33</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>13.83</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44405</v>
+        <v>44406</v>
       </c>
       <c r="H18" t="n">
-        <v>4415.65</v>
+        <v>4234.65</v>
       </c>
       <c r="I18" t="n">
         <v>4317.925462787536</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K18" t="n">
-        <v>9.470000000000001</v>
+        <v>4.98</v>
       </c>
       <c r="L18" t="n">
         <v>5.4</v>
@@ -1467,7 +1682,7 @@
         <v>1.51</v>
       </c>
       <c r="N18" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O18" t="n">
         <v>3.56</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>4</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>12.06</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44440</v>
+        <v>44441</v>
       </c>
       <c r="H19" t="n">
-        <v>4142.7</v>
+        <v>4294.25</v>
       </c>
       <c r="I19" t="n">
         <v>4187.047923638845</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K19" t="n">
-        <v>2.17</v>
+        <v>-1.41</v>
       </c>
       <c r="L19" t="n">
         <v>5.04</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>11.12</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>44491</v>
+        <v>44494</v>
       </c>
       <c r="H20" t="n">
-        <v>5112.05</v>
+        <v>4831.2</v>
       </c>
       <c r="I20" t="n">
         <v>5093.918815207859</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K20" t="n">
-        <v>19.04</v>
+        <v>12.5</v>
       </c>
       <c r="L20" t="n">
         <v>7.02</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,25 +1868,25 @@
         <v>23.52</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>44540</v>
+        <v>44543</v>
       </c>
       <c r="H21" t="n">
-        <v>5544.45</v>
+        <v>5708.5</v>
       </c>
       <c r="I21" t="n">
         <v>5686.411806351728</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K21" t="n">
-        <v>-14.76</v>
+        <v>-18.16</v>
       </c>
       <c r="L21" t="n">
-        <v>18.49</v>
+        <v>21.26</v>
       </c>
       <c r="M21" t="n">
-        <v>1.14</v>
+        <v>1.36</v>
       </c>
       <c r="N21" t="n">
         <v>6.83</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>9.789999999999999</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>44581</v>
+        <v>44582</v>
       </c>
       <c r="H22" t="n">
-        <v>5226.25</v>
+        <v>4979.25</v>
       </c>
       <c r="I22" t="n">
         <v>5149.516574634628</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K22" t="n">
-        <v>-8.449999999999999</v>
+        <v>-12.77</v>
       </c>
       <c r="L22" t="n">
-        <v>11.45</v>
+        <v>13.44</v>
       </c>
       <c r="M22" t="n">
         <v>2.48</v>
       </c>
       <c r="N22" t="n">
-        <v>3.14</v>
+        <v>4.73</v>
       </c>
       <c r="O22" t="n">
         <v>2.96</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>11.08</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>44655</v>
+        <v>44656</v>
       </c>
       <c r="H23" t="n">
-        <v>4404.35</v>
+        <v>4638.7</v>
       </c>
       <c r="I23" t="n">
         <v>4583.200834583518</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K23" t="n">
-        <v>11.55</v>
+        <v>6.84</v>
       </c>
       <c r="L23" t="n">
         <v>4.98</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>4</v>
+      </c>
+      <c r="U23" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>12.06</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>44680</v>
+        <v>44683</v>
       </c>
       <c r="H24" t="n">
-        <v>4396.25</v>
+        <v>3994.85</v>
       </c>
       <c r="I24" t="n">
         <v>4160.749365557873</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K24" t="n">
-        <v>-5.23</v>
+        <v>-13.88</v>
       </c>
       <c r="L24" t="n">
-        <v>10.68</v>
+        <v>14.46</v>
       </c>
       <c r="M24" t="n">
-        <v>1.04</v>
+        <v>4.21</v>
       </c>
       <c r="N24" t="n">
-        <v>2.81</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="O24" t="n">
         <v>5.32</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>13.88</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>44711</v>
+        <v>44712</v>
       </c>
       <c r="H25" t="n">
-        <v>3804.05</v>
+        <v>3858.7</v>
       </c>
       <c r="I25" t="n">
         <v>3834.642160381038</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K25" t="n">
-        <v>4.78</v>
+        <v>3.41</v>
       </c>
       <c r="L25" t="n">
         <v>6.83</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>17.65</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>44769</v>
+        <v>44770</v>
       </c>
       <c r="H26" t="n">
-        <v>3700.25</v>
+        <v>3578.5</v>
       </c>
       <c r="I26" t="n">
         <v>3584.764804208729</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K26" t="n">
-        <v>-4.11</v>
+        <v>-7.26</v>
       </c>
       <c r="L26" t="n">
         <v>15.77</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>12.16</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>44790</v>
+        <v>44791</v>
       </c>
       <c r="H27" t="n">
-        <v>4006.15</v>
+        <v>4068.15</v>
       </c>
       <c r="I27" t="n">
         <v>4013.670033012787</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K27" t="n">
-        <v>-11.95</v>
+        <v>-13.68</v>
       </c>
       <c r="L27" t="n">
-        <v>13.32</v>
+        <v>15.08</v>
       </c>
       <c r="M27" t="n">
         <v>1.15</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>9.26</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>44827</v>
+        <v>44830</v>
       </c>
       <c r="H28" t="n">
-        <v>4314.35</v>
+        <v>4174.05</v>
       </c>
       <c r="I28" t="n">
         <v>4219.024188321035</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K28" t="n">
-        <v>6.05</v>
+        <v>2.6</v>
       </c>
       <c r="L28" t="n">
         <v>4.75</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>11.43</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>44986</v>
+        <v>44987</v>
       </c>
       <c r="H29" t="n">
-        <v>2929.9</v>
+        <v>2949.55</v>
       </c>
       <c r="I29" t="n">
         <v>2939.272737411683</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K29" t="n">
-        <v>29.81</v>
+        <v>29.34</v>
       </c>
       <c r="L29" t="n">
         <v>11.76</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>109</v>
+        <v>110</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>7</v>
+      </c>
+      <c r="U29" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>10.23</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45128</v>
+        <v>45131</v>
       </c>
       <c r="H30" t="n">
-        <v>4176.4</v>
+        <v>4014.85</v>
       </c>
       <c r="I30" t="n">
         <v>4170.130395523696</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="K30" t="n">
-        <v>41.59</v>
+        <v>36.12</v>
       </c>
       <c r="L30" t="n">
         <v>6.63</v>
@@ -2151,7 +2510,7 @@
         <v>1.76</v>
       </c>
       <c r="N30" t="n">
-        <v>3.49</v>
+        <v>3.87</v>
       </c>
       <c r="O30" t="n">
         <v>0.67</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>95</v>
+        <v>96</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>5</v>
+      </c>
+      <c r="U30" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>10.57</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45140</v>
+        <v>45141</v>
       </c>
       <c r="H31" t="n">
-        <v>4127.3</v>
+        <v>4443.35</v>
       </c>
       <c r="I31" t="n">
         <v>4388.775417887025</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K31" t="n">
-        <v>-2.8</v>
+        <v>-10.67</v>
       </c>
       <c r="L31" t="n">
-        <v>5.36</v>
+        <v>11.71</v>
       </c>
       <c r="M31" t="n">
         <v>0.75</v>
       </c>
       <c r="N31" t="n">
-        <v>2.44</v>
+        <v>7.66</v>
       </c>
       <c r="O31" t="n">
         <v>-3.87</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>13.36</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45226</v>
+        <v>45229</v>
       </c>
       <c r="H32" t="n">
-        <v>5374.75</v>
+        <v>5103.85</v>
       </c>
       <c r="I32" t="n">
         <v>5151.855623208134</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="K32" t="n">
-        <v>20.96</v>
+        <v>14.86</v>
       </c>
       <c r="L32" t="n">
         <v>7.93</v>
@@ -2265,7 +2648,7 @@
         <v>1.88</v>
       </c>
       <c r="N32" t="n">
-        <v>2.74</v>
+        <v>5.04</v>
       </c>
       <c r="O32" t="n">
         <v>7.66</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>4</v>
+      </c>
+      <c r="U32" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>11.38</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="H33" t="n">
-        <v>5510.6</v>
+        <v>5951.65</v>
       </c>
       <c r="I33" t="n">
         <v>5587.483952436982</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K33" t="n">
-        <v>-7.97</v>
+        <v>-16.61</v>
       </c>
       <c r="L33" t="n">
-        <v>9.550000000000001</v>
+        <v>18.24</v>
       </c>
       <c r="M33" t="n">
         <v>1</v>
       </c>
       <c r="N33" t="n">
-        <v>3.29</v>
+        <v>8</v>
       </c>
       <c r="O33" t="n">
         <v>-5.04</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>11.25</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45310</v>
+        <v>45311</v>
       </c>
       <c r="H34" t="n">
-        <v>6100.2</v>
+        <v>6019.2</v>
       </c>
       <c r="I34" t="n">
         <v>6079.728627132185</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K34" t="n">
-        <v>2.5</v>
+        <v>1.13</v>
       </c>
       <c r="L34" t="n">
         <v>7.35</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>10.39</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45338</v>
+        <v>45341</v>
       </c>
       <c r="H35" t="n">
-        <v>6378.1</v>
+        <v>6743.85</v>
       </c>
       <c r="I35" t="n">
         <v>6424.156067010149</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K35" t="n">
-        <v>-5.96</v>
+        <v>-12.04</v>
       </c>
       <c r="L35" t="n">
-        <v>7.52</v>
+        <v>13.14</v>
       </c>
       <c r="M35" t="n">
         <v>2.84</v>
       </c>
       <c r="N35" t="n">
-        <v>2.22</v>
+        <v>5.73</v>
       </c>
       <c r="O35" t="n">
         <v>-1.33</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>10.53</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45446</v>
+        <v>45447</v>
       </c>
       <c r="H36" t="n">
-        <v>9886</v>
+        <v>8851.4</v>
       </c>
       <c r="I36" t="n">
         <v>8908.011536580814</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K36" t="n">
-        <v>46.59</v>
+        <v>31.25</v>
       </c>
       <c r="L36" t="n">
         <v>4.95</v>
@@ -2493,7 +2924,7 @@
         <v>2.96</v>
       </c>
       <c r="N36" t="n">
-        <v>4.22</v>
+        <v>10.47</v>
       </c>
       <c r="O36" t="n">
         <v>5.73</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>5</v>
+      </c>
+      <c r="U36" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>16.74</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45455</v>
+        <v>45456</v>
       </c>
       <c r="H37" t="n">
-        <v>10317.5</v>
+        <v>10855.7</v>
       </c>
       <c r="I37" t="n">
         <v>10333.45211707727</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K37" t="n">
-        <v>-16.56</v>
+        <v>-22.64</v>
       </c>
       <c r="L37" t="n">
-        <v>16.91</v>
+        <v>23.02</v>
       </c>
       <c r="M37" t="n">
         <v>2.81</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>12.86</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45491</v>
+        <v>45492</v>
       </c>
       <c r="H38" t="n">
-        <v>11945.85</v>
+        <v>11267.2</v>
       </c>
       <c r="I38" t="n">
         <v>11670.42716025631</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K38" t="n">
-        <v>10.04</v>
+        <v>3.79</v>
       </c>
       <c r="L38" t="n">
         <v>4.62</v>
@@ -2607,7 +3062,7 @@
         <v>0.57</v>
       </c>
       <c r="N38" t="n">
-        <v>4.83</v>
+        <v>5.68</v>
       </c>
       <c r="O38" t="n">
         <v>5.22</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>13.83</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45518</v>
+        <v>45520</v>
       </c>
       <c r="H39" t="n">
-        <v>11913.9</v>
+        <v>12374.9</v>
       </c>
       <c r="I39" t="n">
         <v>12176.23510935123</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K39" t="n">
-        <v>-5.74</v>
+        <v>-9.83</v>
       </c>
       <c r="L39" t="n">
         <v>12.63</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>12.13</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45540</v>
+        <v>45541</v>
       </c>
       <c r="H40" t="n">
-        <v>12412.2</v>
+        <v>12063.85</v>
       </c>
       <c r="I40" t="n">
         <v>12221.55239805444</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K40" t="n">
-        <v>0.3</v>
+        <v>-2.51</v>
       </c>
       <c r="L40" t="n">
         <v>2.83</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,28 +3248,28 @@
         <v>12.29</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45548</v>
+        <v>45551</v>
       </c>
       <c r="H41" t="n">
-        <v>13027.65</v>
+        <v>13990.3</v>
       </c>
       <c r="I41" t="n">
         <v>13513.88190596936</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K41" t="n">
-        <v>-7.99</v>
+        <v>-15.97</v>
       </c>
       <c r="L41" t="n">
-        <v>8.75</v>
+        <v>16.51</v>
       </c>
       <c r="M41" t="n">
         <v>2.21</v>
       </c>
       <c r="N41" t="n">
-        <v>2.8</v>
+        <v>7.39</v>
       </c>
       <c r="O41" t="n">
         <v>-2.81</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>13.19</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45589</v>
+        <v>45590</v>
       </c>
       <c r="H42" t="n">
-        <v>15055.3</v>
+        <v>13937.2</v>
       </c>
       <c r="I42" t="n">
         <v>14190.44786584379</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K42" t="n">
-        <v>7.61</v>
+        <v>-0.38</v>
       </c>
       <c r="L42" t="n">
         <v>6.72</v>
@@ -2835,7 +3338,7 @@
         <v>2.13</v>
       </c>
       <c r="N42" t="n">
-        <v>4.06</v>
+        <v>7.43</v>
       </c>
       <c r="O42" t="n">
         <v>7.39</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>19</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45625</v>
+        <v>45628</v>
       </c>
       <c r="H43" t="n">
-        <v>15807.4</v>
+        <v>16763.9</v>
       </c>
       <c r="I43" t="n">
         <v>16167.92352255869</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K43" t="n">
-        <v>-13.42</v>
+        <v>-20.28</v>
       </c>
       <c r="L43" t="n">
-        <v>14.71</v>
+        <v>20.85</v>
       </c>
       <c r="M43" t="n">
         <v>5.61</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>11.97</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45664</v>
+        <v>45665</v>
       </c>
       <c r="H44" t="n">
-        <v>18451.85</v>
+        <v>16905.85</v>
       </c>
       <c r="I44" t="n">
         <v>17462.07084832315</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K44" t="n">
-        <v>10.07</v>
+        <v>0.85</v>
       </c>
       <c r="L44" t="n">
         <v>4.44</v>
@@ -2949,7 +3476,7 @@
         <v>2.2</v>
       </c>
       <c r="N44" t="n">
-        <v>2.72</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="O44" t="n">
         <v>6.05</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>15.38</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45758</v>
+        <v>45762</v>
       </c>
       <c r="H45" t="n">
-        <v>14301.9</v>
+        <v>14931</v>
       </c>
       <c r="I45" t="n">
         <v>14393.05179914741</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="K45" t="n">
-        <v>15.4</v>
+        <v>11.68</v>
       </c>
       <c r="L45" t="n">
         <v>9.1</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>4</v>
+      </c>
+      <c r="U45" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>14.55</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45799</v>
+        <v>45800</v>
       </c>
       <c r="H46" t="n">
-        <v>15170</v>
+        <v>15019</v>
       </c>
       <c r="I46" t="n">
         <v>15093.45772600635</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K46" t="n">
-        <v>1.6</v>
+        <v>0.59</v>
       </c>
       <c r="L46" t="n">
         <v>2.87</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>12.55</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45839</v>
+        <v>45840</v>
       </c>
       <c r="H47" t="n">
-        <v>14716</v>
+        <v>15163</v>
       </c>
       <c r="I47" t="n">
         <v>15113.28619227923</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K47" t="n">
-        <v>2.02</v>
+        <v>-0.96</v>
       </c>
       <c r="L47" t="n">
         <v>1.84</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>11.58</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45880</v>
+        <v>45881</v>
       </c>
       <c r="H48" t="n">
-        <v>16088</v>
+        <v>15828</v>
       </c>
       <c r="I48" t="n">
         <v>15835.3003229574</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K48" t="n">
-        <v>6.1</v>
+        <v>4.39</v>
       </c>
       <c r="L48" t="n">
         <v>3.2</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>8.859999999999999</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45898</v>
+        <v>45901</v>
       </c>
       <c r="H49" t="n">
-        <v>16690</v>
+        <v>17582</v>
       </c>
       <c r="I49" t="n">
         <v>17117.77594781047</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K49" t="n">
-        <v>-5.45</v>
+        <v>-11.08</v>
       </c>
       <c r="L49" t="n">
-        <v>9.220000000000001</v>
+        <v>11.46</v>
       </c>
       <c r="M49" t="n">
         <v>1.91</v>
       </c>
       <c r="N49" t="n">
-        <v>3.49</v>
+        <v>5.34</v>
       </c>
       <c r="O49" t="n">
         <v>-1.62</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>9.68</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="H50" t="n">
-        <v>18202</v>
+        <v>17511</v>
       </c>
       <c r="I50" t="n">
         <v>17522.23765532314</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K50" t="n">
-        <v>3.53</v>
+        <v>-0.4</v>
       </c>
       <c r="L50" t="n">
         <v>4.62</v>
@@ -3291,7 +3890,7 @@
         <v>0.17</v>
       </c>
       <c r="N50" t="n">
-        <v>0.84</v>
+        <v>3.8</v>
       </c>
       <c r="O50" t="n">
         <v>5.34</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>7.19</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="H51" t="n">
-        <v>11031</v>
+        <v>11678</v>
       </c>
       <c r="I51" t="n">
         <v>11465.50291505025</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K51" t="n">
-        <v>37.01</v>
+        <v>33.31</v>
       </c>
       <c r="L51" t="n">
         <v>4.1</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>88</v>
+        <v>89</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>6</v>
+      </c>
+      <c r="U51" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="52">
@@ -3384,22 +4007,22 @@
         <v>18.02</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="H52" t="n">
-        <v>10525</v>
+        <v>10388</v>
       </c>
       <c r="I52" t="n">
         <v>10424.56608795658</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K52" t="n">
-        <v>-9.869999999999999</v>
+        <v>-11.05</v>
       </c>
       <c r="L52" t="n">
-        <v>11.19</v>
+        <v>11.63</v>
       </c>
       <c r="M52" t="n">
         <v>1.08</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>12.79</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46125</v>
+        <v>46127</v>
       </c>
       <c r="H53" t="n">
-        <v>10503.5</v>
+        <v>11068.5</v>
       </c>
       <c r="I53" t="n">
         <v>10980.84754986841</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K53" t="n">
-        <v>-1.11</v>
+        <v>-6.55</v>
       </c>
       <c r="L53" t="n">
-        <v>6.64</v>
+        <v>6.84</v>
       </c>
       <c r="M53" t="n">
         <v>6.07</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,28 +4145,28 @@
         <v>13.51</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="H54" t="n">
-        <v>10772</v>
+        <v>10138</v>
       </c>
       <c r="I54" t="n">
         <v>10327.02070603071</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K54" t="n">
-        <v>-2.68</v>
+        <v>-8.41</v>
       </c>
       <c r="L54" t="n">
-        <v>4.8</v>
+        <v>8.75</v>
       </c>
       <c r="M54" t="n">
         <v>0.28</v>
       </c>
       <c r="N54" t="n">
-        <v>3.55</v>
+        <v>5.89</v>
       </c>
       <c r="O54" t="n">
         <v>5.38</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>15.34</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="H55" t="n">
-        <v>11258</v>
+        <v>11722</v>
       </c>
       <c r="I55" t="n">
         <v>11693.48896329593</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K55" t="n">
-        <v>-11.05</v>
+        <v>-15.62</v>
       </c>
       <c r="L55" t="n">
-        <v>12.05</v>
+        <v>16.99</v>
       </c>
       <c r="M55" t="n">
         <v>1.15</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>12.85</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="H56" t="n">
-        <v>13845</v>
+        <v>13500</v>
       </c>
       <c r="I56" t="n">
         <v>13688.92041584365</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K56" t="n">
-        <v>18.11</v>
+        <v>15.17</v>
       </c>
       <c r="L56" t="n">
         <v>4.85</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>5</v>
+      </c>
+      <c r="U56" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="57">
@@ -3693,6 +4376,14 @@
       <c r="Q57" t="n">
         <v>32</v>
       </c>
+      <c r="R57" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7563,7 +8254,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>57.7</v>
+        <v>59.3</v>
       </c>
     </row>
     <row r="6">
@@ -7573,7 +8264,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7">
@@ -7583,7 +8274,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>190</v>
+        <v>194</v>
       </c>
     </row>
     <row r="8">
@@ -7593,7 +8284,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
@@ -7603,7 +8294,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10">
@@ -7613,7 +8304,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>126</v>
+        <v>128.2</v>
       </c>
     </row>
     <row r="11">
@@ -7623,7 +8314,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12">
@@ -7633,7 +8324,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13">
@@ -7643,7 +8334,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>30.9</v>
+        <v>29.1</v>
       </c>
     </row>
     <row r="14">
@@ -7653,7 +8344,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>9.710000000000001</v>
+        <v>4.67</v>
       </c>
     </row>
     <row r="15">
@@ -7663,7 +8354,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17.69</v>
+        <v>12.65</v>
       </c>
     </row>
     <row r="16">
@@ -7673,7 +8364,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.44</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="17">
@@ -7683,7 +8374,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>112.27</v>
+        <v>103.96</v>
       </c>
     </row>
     <row r="18">
@@ -7693,7 +8384,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>60</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="19">
@@ -7703,7 +8394,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8.08</v>
+        <v>9.48</v>
       </c>
     </row>
     <row r="20">
@@ -7713,7 +8404,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7.02</v>
+        <v>8.25</v>
       </c>
     </row>
     <row r="21">
@@ -7723,7 +8414,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>18.49</v>
+        <v>23.02</v>
       </c>
     </row>
     <row r="22">
@@ -7733,7 +8424,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="23">
@@ -7743,7 +8434,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24">
@@ -7753,7 +8444,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.36</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="25">
@@ -7773,7 +8464,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5.09</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="27">
@@ -7783,7 +8474,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>12.29</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="28">
@@ -7793,7 +8484,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
     </row>
     <row r="29">
